--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aumovio-my.sharepoint.com/personal/uidv9144_automotive-wan_com/Documents/Y 2026/VIO/SAM China Communication Dashboard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aumovio-my.sharepoint.com/personal/uik07697_automotive-wan_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{E5364B93-5AA3-4605-BAC9-40A0709A34CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{667EC899-FCF7-4BBA-869F-6D537D98DA7C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDAD08D9-3D4E-476C-AF3A-170A20D1DE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026 old'!$A$2:$F$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$2:$F$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$2:$F$60</definedName>
   </definedNames>
   <calcPr calcId="191028" concurrentManualCount="12"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="96">
   <si>
     <t>Year</t>
   </si>
@@ -320,6 +320,15 @@
   </si>
   <si>
     <t>delay</t>
+  </si>
+  <si>
+    <t>Braking Safety - The Permanent Focus on Every Journey</t>
+  </si>
+  <si>
+    <t>Topic Discussion: MAEXTRO V800 Brake Incident: Our Reflections for Mechanical Safety in Intelligent Vehicles</t>
+  </si>
+  <si>
+    <t>Topic Discussion: In the next 3-5 years, will AI be a competitive advantage or a cost burden for AUMOVIO?</t>
   </si>
 </sst>
 </file>
@@ -977,8 +986,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{87AE0588-74B1-435D-89DA-BDDFAE4D4F08}" name="Table13" displayName="Table13" ref="A2:I87" totalsRowShown="0" headerRowDxfId="25" dataDxfId="23" headerRowBorderDxfId="24" tableBorderDxfId="22">
-  <autoFilter ref="A2:I87" xr:uid="{4AF62893-D76B-41CA-862A-2A0CA5F92DCA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{87AE0588-74B1-435D-89DA-BDDFAE4D4F08}" name="Table13" displayName="Table13" ref="A2:I90" totalsRowShown="0" headerRowDxfId="25" dataDxfId="23" headerRowBorderDxfId="24" tableBorderDxfId="22">
+  <autoFilter ref="A2:I90" xr:uid="{4AF62893-D76B-41CA-862A-2A0CA5F92DCA}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{887A09BA-E193-41CE-830F-B59E6BD137A0}" name="Year" dataDxfId="21"/>
     <tableColumn id="2" xr3:uid="{63EC88A9-C4E0-409C-8163-247BDCC14BC5}" name="Month" dataDxfId="20"/>
@@ -1275,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C514591A-F47A-421D-8C5F-2D1DE3B987E2}">
-  <dimension ref="A2:I87"/>
+  <dimension ref="A2:I90"/>
   <sheetFormatPr defaultColWidth="9.81640625" defaultRowHeight="15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="2" customWidth="1"/>
@@ -2191,28 +2200,24 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="10">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C39" s="11">
-        <v>46269</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>15</v>
+        <v>46265</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>11</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F39" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="G39" s="15"/>
-      <c r="H39" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" s="2"/>
+      <c r="F39" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G39" s="1"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="10">
@@ -2224,19 +2229,20 @@
       <c r="C40" s="11">
         <v>46269</v>
       </c>
-      <c r="D40" s="12" t="s">
-        <v>11</v>
+      <c r="D40" s="14" t="s">
+        <v>15</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G40" s="1"/>
-      <c r="I40" s="2" t="s">
-        <v>91</v>
-      </c>
+      <c r="F40" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="G40" s="15"/>
+      <c r="H40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" s="2"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="10">
@@ -2246,7 +2252,7 @@
         <v>52</v>
       </c>
       <c r="C41" s="11">
-        <v>46281</v>
+        <v>46269</v>
       </c>
       <c r="D41" s="12" t="s">
         <v>11</v>
@@ -2254,11 +2260,13 @@
       <c r="E41" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F41" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
+      <c r="F41" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G41" s="1"/>
+      <c r="I41" s="2" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="10">
@@ -2270,8 +2278,8 @@
       <c r="C42" s="11">
         <v>46281</v>
       </c>
-      <c r="D42" s="14" t="s">
-        <v>15</v>
+      <c r="D42" s="12" t="s">
+        <v>11</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>12</v>
@@ -2279,12 +2287,7 @@
       <c r="F42" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G42" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="H42" s="2"/>
       <c r="I42" s="2"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
@@ -2295,19 +2298,23 @@
         <v>52</v>
       </c>
       <c r="C43" s="11">
-        <v>46285</v>
-      </c>
-      <c r="D43" s="12" t="s">
-        <v>11</v>
+        <v>46281</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>15</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G43" s="15"/>
-      <c r="H43" s="15"/>
+        <v>55</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="I43" s="2"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
@@ -2320,8 +2327,8 @@
       <c r="C44" s="11">
         <v>46285</v>
       </c>
-      <c r="D44" s="14" t="s">
-        <v>15</v>
+      <c r="D44" s="12" t="s">
+        <v>11</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>17</v>
@@ -2329,10 +2336,8 @@
       <c r="F44" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G44" s="1"/>
-      <c r="H44" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="G44" s="15"/>
+      <c r="H44" s="15"/>
       <c r="I44" s="2"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
@@ -2343,16 +2348,16 @@
         <v>52</v>
       </c>
       <c r="C45" s="11">
-        <v>46290</v>
+        <v>46285</v>
       </c>
       <c r="D45" s="14" t="s">
         <v>15</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="2" t="s">
@@ -2360,49 +2365,51 @@
       </c>
       <c r="I45" s="2"/>
     </row>
-    <row r="46" spans="1:9" ht="30" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" s="10">
         <v>2026</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C46" s="11">
+        <v>46290</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G46" s="1"/>
+      <c r="H46" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46" s="2"/>
+    </row>
+    <row r="47" spans="1:9" ht="30" x14ac:dyDescent="0.35">
+      <c r="A47" s="10">
+        <v>2026</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C47" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D46" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F46" s="13" t="s">
+      <c r="D47" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="G46" s="1"/>
-      <c r="I46" s="2"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A47" s="10">
-        <v>2026</v>
-      </c>
-      <c r="B47" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C47" s="11">
-        <v>46311</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G47" s="15"/>
-      <c r="H47" s="15"/>
+      <c r="G47" s="1"/>
       <c r="I47" s="2"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
@@ -2413,20 +2420,18 @@
         <v>60</v>
       </c>
       <c r="C48" s="11">
-        <v>46318</v>
+        <v>46305</v>
       </c>
       <c r="D48" s="12" t="s">
         <v>11</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F48" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="G48" s="15"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G48" s="1"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" s="10">
@@ -2436,7 +2441,7 @@
         <v>60</v>
       </c>
       <c r="C49" s="11">
-        <v>46321</v>
+        <v>46311</v>
       </c>
       <c r="D49" s="12" t="s">
         <v>11</v>
@@ -2445,7 +2450,7 @@
         <v>12</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G49" s="15"/>
       <c r="H49" s="15"/>
@@ -2459,19 +2464,19 @@
         <v>60</v>
       </c>
       <c r="C50" s="11">
-        <v>46321</v>
+        <v>46318</v>
       </c>
       <c r="D50" s="12" t="s">
         <v>11</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>64</v>
+        <v>17</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>62</v>
       </c>
       <c r="G50" s="15"/>
-      <c r="H50" s="15"/>
+      <c r="H50" s="2"/>
       <c r="I50" s="2"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
@@ -2491,7 +2496,7 @@
         <v>12</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G51" s="15"/>
       <c r="H51" s="15"/>
@@ -2505,21 +2510,19 @@
         <v>60</v>
       </c>
       <c r="C52" s="11">
-        <v>46311</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>15</v>
+        <v>46321</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>11</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G52" s="1"/>
-      <c r="H52" s="2" t="s">
-        <v>16</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="G52" s="15"/>
+      <c r="H52" s="15"/>
       <c r="I52" s="2"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
@@ -2530,23 +2533,19 @@
         <v>60</v>
       </c>
       <c r="C53" s="11">
-        <v>46318</v>
-      </c>
-      <c r="D53" s="14" t="s">
-        <v>15</v>
+        <v>46321</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>11</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F53" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>16</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G53" s="15"/>
+      <c r="H53" s="15"/>
       <c r="I53" s="2"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
@@ -2557,22 +2556,20 @@
         <v>60</v>
       </c>
       <c r="C54" s="11">
-        <v>46321</v>
+        <v>46308</v>
       </c>
       <c r="D54" s="14" t="s">
         <v>15</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G54" s="1"/>
-      <c r="H54" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I54" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" s="10">
@@ -2582,7 +2579,7 @@
         <v>60</v>
       </c>
       <c r="C55" s="11">
-        <v>46321</v>
+        <v>46311</v>
       </c>
       <c r="D55" s="14" t="s">
         <v>15</v>
@@ -2591,7 +2588,7 @@
         <v>12</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="2" t="s">
@@ -2607,18 +2604,20 @@
         <v>60</v>
       </c>
       <c r="C56" s="11">
-        <v>46321</v>
+        <v>46318</v>
       </c>
       <c r="D56" s="14" t="s">
         <v>15</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G56" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="F56" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="H56" s="2" t="s">
         <v>16</v>
       </c>
@@ -2631,8 +2630,8 @@
       <c r="B57" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>66</v>
+      <c r="C57" s="11">
+        <v>46321</v>
       </c>
       <c r="D57" s="14" t="s">
         <v>15</v>
@@ -2641,11 +2640,9 @@
         <v>12</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>16</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="G57" s="1"/>
       <c r="H57" s="2" t="s">
         <v>16</v>
       </c>
@@ -2656,21 +2653,24 @@
         <v>2026</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>11</v>
+        <v>60</v>
+      </c>
+      <c r="C58" s="11">
+        <v>46321</v>
+      </c>
+      <c r="D58" s="14" t="s">
+        <v>15</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G58" s="1"/>
+      <c r="H58" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="I58" s="2"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
@@ -2678,23 +2678,21 @@
         <v>2026</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
+      </c>
+      <c r="C59" s="11">
+        <v>46321</v>
       </c>
       <c r="D59" s="14" t="s">
         <v>15</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>16</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="G59" s="1"/>
       <c r="H59" s="2" t="s">
         <v>16</v>
       </c>
@@ -2702,69 +2700,78 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" s="10">
-        <v>2027</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>14</v>
+        <v>2026</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>60</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>11</v>
+        <v>66</v>
+      </c>
+      <c r="D60" s="14" t="s">
+        <v>15</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F60" s="13" t="s">
-        <v>72</v>
+      <c r="F60" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="I60" s="2"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="10">
-        <v>2027</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>14</v>
+        <v>2026</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>70</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D61" s="14" t="s">
-        <v>15</v>
+        <v>66</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>11</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F61" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>16</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G61" s="1"/>
       <c r="I61" s="2"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" s="10">
-        <v>2027</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>26</v>
+        <v>2026</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>70</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>11</v>
+        <v>66</v>
+      </c>
+      <c r="D62" s="14" t="s">
+        <v>15</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G62" s="1"/>
+        <v>71</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="I62" s="2"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.35">
@@ -2772,25 +2779,19 @@
         <v>2027</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D63" s="14" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>11</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="F63" s="13" t="s">
+        <v>72</v>
       </c>
       <c r="I63" s="2"/>
     </row>
@@ -2798,82 +2799,128 @@
       <c r="A64" s="10">
         <v>2027</v>
       </c>
-      <c r="B64" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C64" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D64" s="12" t="s">
-        <v>11</v>
+      <c r="B64" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D64" s="14" t="s">
+        <v>15</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G64" s="15"/>
-      <c r="H64" s="15"/>
-      <c r="I64" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F64" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I64" s="2"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" s="10">
         <v>2027</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B65" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G65" s="1"/>
+      <c r="I65" s="2"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A66" s="10">
+        <v>2027</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D66" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I66" s="2"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A67" s="10">
+        <v>2027</v>
+      </c>
+      <c r="B67" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C65" s="10" t="s">
+      <c r="C67" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D65" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F65" s="2" t="s">
+      <c r="D67" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F67" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G65" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I65" s="2" t="s">
+      <c r="G67" s="15"/>
+      <c r="H67" s="15"/>
+      <c r="I67" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A66" s="1"/>
-      <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A67" s="1"/>
-      <c r="B67" s="1"/>
-      <c r="C67" s="1"/>
-      <c r="D67" s="1"/>
-      <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-    </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
-      <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
+      <c r="A68" s="10">
+        <v>2027</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D68" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" s="1"/>
@@ -2990,6 +3037,9 @@
     <row r="85" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="86" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="87" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="88" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="89" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="90" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aumovio-my.sharepoint.com/personal/uik07697_automotive-wan_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDAD08D9-3D4E-476C-AF3A-170A20D1DE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{DDAD08D9-3D4E-476C-AF3A-170A20D1DE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26DAD7D9-BBC0-4216-9861-C935275B1202}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="6" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="97">
   <si>
     <t>Year</t>
   </si>
@@ -329,6 +329,9 @@
   </si>
   <si>
     <t>Topic Discussion: In the next 3-5 years, will AI be a competitive advantage or a cost burden for AUMOVIO?</t>
+  </si>
+  <si>
+    <t>NOV</t>
   </si>
 </sst>
 </file>
@@ -2203,7 +2206,7 @@
         <v>2027</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C39" s="11">
         <v>46265</v>
@@ -2628,10 +2631,10 @@
         <v>2026</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C57" s="11">
-        <v>46321</v>
+        <v>96</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>96</v>
       </c>
       <c r="D57" s="14" t="s">
         <v>15</v>
@@ -2653,10 +2656,10 @@
         <v>2026</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C58" s="11">
-        <v>46321</v>
+        <v>96</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>96</v>
       </c>
       <c r="D58" s="14" t="s">
         <v>15</v>
@@ -2705,8 +2708,8 @@
       <c r="B60" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>66</v>
+      <c r="C60" s="10" t="s">
+        <v>60</v>
       </c>
       <c r="D60" s="14" t="s">
         <v>15</v>
@@ -2732,8 +2735,8 @@
       <c r="B61" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>66</v>
+      <c r="C61" s="10" t="s">
+        <v>70</v>
       </c>
       <c r="D61" s="12" t="s">
         <v>11</v>
@@ -2754,8 +2757,8 @@
       <c r="B62" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>66</v>
+      <c r="C62" s="10" t="s">
+        <v>70</v>
       </c>
       <c r="D62" s="14" t="s">
         <v>15</v>
@@ -2778,10 +2781,10 @@
       <c r="A63" s="10">
         <v>2027</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="10" t="s">
         <v>14</v>
       </c>
       <c r="D63" s="12" t="s">
@@ -2799,10 +2802,10 @@
       <c r="A64" s="10">
         <v>2027</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="10" t="s">
         <v>14</v>
       </c>
       <c r="D64" s="14" t="s">
@@ -2823,10 +2826,10 @@
       <c r="A65" s="10">
         <v>2027</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="D65" s="12" t="s">
@@ -2845,7 +2848,7 @@
       <c r="A66" s="10">
         <v>2027</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="10" t="s">
         <v>26</v>
       </c>
       <c r="C66" s="2" t="s">
@@ -2924,7 +2927,7 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
+      <c r="B69" s="10"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
@@ -2933,7 +2936,7 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" s="1"/>
-      <c r="B70" s="1"/>
+      <c r="B70" s="10"/>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
@@ -2942,7 +2945,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" s="1"/>
-      <c r="B71" s="1"/>
+      <c r="B71" s="10"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aumovio-my.sharepoint.com/personal/uik07697_automotive-wan_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{DDAD08D9-3D4E-476C-AF3A-170A20D1DE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26DAD7D9-BBC0-4216-9861-C935275B1202}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{DDAD08D9-3D4E-476C-AF3A-170A20D1DE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA2AC7C3-7421-4A1A-B026-37EFA1E402BA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2203,7 +2203,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="10">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B39" s="10" t="s">
         <v>43</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aumovio-my.sharepoint.com/personal/uik07697_automotive-wan_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{DDAD08D9-3D4E-476C-AF3A-170A20D1DE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA2AC7C3-7421-4A1A-B026-37EFA1E402BA}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{DDAD08D9-3D4E-476C-AF3A-170A20D1DE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4383AD6A-D72A-4129-A56A-79DA65184512}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="97">
   <si>
     <t>Year</t>
   </si>
@@ -2487,10 +2487,10 @@
         <v>2026</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C51" s="11">
-        <v>46321</v>
+        <v>68</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>68</v>
       </c>
       <c r="D51" s="12" t="s">
         <v>11</v>
@@ -2510,10 +2510,10 @@
         <v>2026</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C52" s="11">
-        <v>46321</v>
+        <v>68</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>68</v>
       </c>
       <c r="D52" s="12" t="s">
         <v>11</v>
